--- a/12619425.xlsx
+++ b/12619425.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{198C38EB-A997-4217-9A48-5B5EE25545EE}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD88A766-ADC9-4491-B754-4F05B73901E4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,18 @@
   </si>
   <si>
     <t>cooked tasty chicken</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>boring day</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>semi final day</t>
   </si>
 </sst>
 </file>
@@ -1388,7 +1400,7 @@
         <v>45</v>
       </c>
       <c r="F13" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G13" s="14">
         <v>6</v>
@@ -1398,11 +1410,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1285</v>
+        <v>1235</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>58</v>
@@ -1434,7 +1446,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G14" s="14">
         <v>6</v>
@@ -1444,11 +1456,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1170</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>61</v>
@@ -1480,7 +1492,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G15" s="14">
         <v>6</v>
@@ -1490,11 +1502,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1060</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>58</v>
@@ -1526,7 +1538,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
@@ -1536,11 +1548,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1180</v>
+        <v>1130</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>54</v>
@@ -1572,7 +1584,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G17" s="14">
         <v>5</v>
@@ -1582,11 +1594,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1070</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>54</v>
@@ -2213,7 +2225,7 @@
         <v>120</v>
       </c>
       <c r="E31" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F31" s="14">
         <v>250</v>
@@ -2226,11 +2238,11 @@
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1110</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>61</v>
@@ -2245,93 +2257,189 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:14" ht="15">
+      <c r="A32" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B32" s="14">
+        <v>300</v>
+      </c>
+      <c r="C32" s="14">
+        <v>140</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>200</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15">
+      <c r="A33" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B33" s="14">
+        <v>400</v>
+      </c>
+      <c r="C33" s="14">
+        <v>120</v>
+      </c>
+      <c r="D33" s="14">
+        <v>140</v>
+      </c>
+      <c r="E33" s="14">
+        <v>80</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15">
+      <c r="A34" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>90</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>75</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>250</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>425</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15">
+      <c r="A35" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B35" s="14">
+        <v>360</v>
+      </c>
+      <c r="C35" s="14">
+        <v>200</v>
+      </c>
+      <c r="D35" s="14">
+        <v>80</v>
+      </c>
+      <c r="E35" s="14">
+        <v>55</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>300</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>145</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="13"/>

--- a/12619425.xlsx
+++ b/12619425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD88A766-ADC9-4491-B754-4F05B73901E4}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92CCB13D-CBC2-4D61-9608-E3344069A87B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>semi final day</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -2441,27 +2444,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="15">
+      <c r="A36" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B36" s="14">
+        <v>400</v>
+      </c>
+      <c r="C36" s="14">
+        <v>120</v>
+      </c>
+      <c r="D36" s="14">
+        <v>140</v>
+      </c>
+      <c r="E36" s="14">
+        <v>120</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>220</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="13"/>

--- a/12619425.xlsx
+++ b/12619425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92CCB13D-CBC2-4D61-9608-E3344069A87B}"/>
+  <xr:revisionPtr revIDLastSave="456" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{895EA2C2-11B1-45EC-81D4-CB63DE9492B6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>null</t>
+  </si>
+  <si>
+    <t>back pain</t>
   </si>
 </sst>
 </file>
@@ -2490,27 +2493,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="15">
+      <c r="A37" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B37" s="14">
+        <v>380</v>
+      </c>
+      <c r="C37" s="14">
+        <v>100</v>
+      </c>
+      <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
+        <v>140</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>240</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="13"/>

--- a/12619425.xlsx
+++ b/12619425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="456" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{895EA2C2-11B1-45EC-81D4-CB63DE9492B6}"/>
+  <xr:revisionPtr revIDLastSave="469" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC7BE70E-EEF3-4044-93C7-1CE3C2EA077F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>back pain</t>
+  </si>
+  <si>
+    <t>had a CA today</t>
   </si>
 </sst>
 </file>
@@ -2539,27 +2542,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+    <row r="38" spans="1:14" ht="15">
+      <c r="A38" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>150</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>140</v>
+      </c>
+      <c r="F38" s="14">
+        <v>300</v>
+      </c>
+      <c r="G38" s="14">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14">
+        <v>290</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="13"/>

--- a/12619425.xlsx
+++ b/12619425.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="469" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC7BE70E-EEF3-4044-93C7-1CE3C2EA077F}"/>
+  <xr:revisionPtr revIDLastSave="506" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4095D86B-1114-4F9C-BB6E-2C8926EBD7F8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,12 @@
   </si>
   <si>
     <t>had a CA today</t>
+  </si>
+  <si>
+    <t>another CA</t>
+  </si>
+  <si>
+    <t>made biryani</t>
   </si>
 </sst>
 </file>
@@ -2588,71 +2594,143 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="39" spans="1:14" ht="15">
+      <c r="A39" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B39" s="14">
+        <v>320</v>
+      </c>
+      <c r="C39" s="14">
+        <v>130</v>
+      </c>
+      <c r="D39" s="14">
+        <v>140</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>200</v>
+      </c>
+      <c r="G39" s="14">
+        <v>4</v>
+      </c>
+      <c r="H39" s="14">
+        <v>220</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+        <v>310</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15">
+      <c r="A40" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B40" s="14">
+        <v>300</v>
+      </c>
+      <c r="C40" s="14">
+        <v>100</v>
+      </c>
+      <c r="D40" s="14">
+        <v>130</v>
+      </c>
+      <c r="E40" s="14">
+        <v>90</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15">
+      <c r="A41" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B41" s="14">
+        <v>320</v>
+      </c>
+      <c r="C41" s="14">
+        <v>130</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>90</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>250</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13"/>

--- a/12619425.xlsx
+++ b/12619425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="506" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4095D86B-1114-4F9C-BB6E-2C8926EBD7F8}"/>
+  <xr:revisionPtr revIDLastSave="520" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A04284F8-2976-4995-9575-CCCA10DCB002}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>made biryani</t>
+  </si>
+  <si>
+    <t>mondays are boring</t>
   </si>
 </sst>
 </file>
@@ -1132,11 +1135,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1383,36 +1386,66 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="15">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+      <c r="A12" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>240</v>
+      </c>
+      <c r="D12" s="14">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14">
+        <v>45</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>230</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="0"/>
+        <v>1235</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="1"/>
+        <v>205</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:17" ht="15">
       <c r="A13" s="13">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="14">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C13" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="D13" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E13" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F13" s="14">
         <v>300</v>
@@ -1421,41 +1454,41 @@
         <v>6</v>
       </c>
       <c r="H13" s="14">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1235</v>
+        <v>1170</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15">
       <c r="A14" s="13">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="C14" s="14">
         <v>120</v>
       </c>
       <c r="D14" s="14">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E14" s="14">
         <v>30</v>
@@ -1467,44 +1500,44 @@
         <v>6</v>
       </c>
       <c r="H14" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1060</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>380</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="30.75">
       <c r="A15" s="13">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C15" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D15" s="14">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="E15" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F15" s="14">
         <v>300</v>
@@ -1513,61 +1546,61 @@
         <v>6</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1130</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="30.75">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15">
       <c r="A16" s="13">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="14">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="C16" s="14">
+        <v>130</v>
+      </c>
+      <c r="D16" s="14">
         <v>100</v>
       </c>
-      <c r="D16" s="14">
-        <v>220</v>
-      </c>
       <c r="E16" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1070</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>54</v>
@@ -1579,116 +1612,116 @@
         <v>56</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
       <c r="A17" s="13">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="14">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="C17" s="14">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="D17" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H17" s="14">
         <v>200</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>790</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>650</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
       <c r="A18" s="13">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="14">
-        <v>290</v>
+        <v>400</v>
       </c>
       <c r="C18" s="14">
+        <v>140</v>
+      </c>
+      <c r="D18" s="14">
+        <v>40</v>
+      </c>
+      <c r="E18" s="14">
         <v>60</v>
       </c>
-      <c r="D18" s="14">
-        <v>60</v>
-      </c>
-      <c r="E18" s="14">
-        <v>30</v>
-      </c>
       <c r="F18" s="14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
       <c r="A19" s="13">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="14">
         <v>400</v>
       </c>
       <c r="C19" s="14">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D19" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E19" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
         <v>0</v>
@@ -1697,15 +1730,15 @@
         <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>54</v>
@@ -1717,41 +1750,41 @@
         <v>56</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15">
       <c r="A20" s="13">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="14">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="C20" s="14">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
         <v>50</v>
       </c>
-      <c r="E20" s="14">
-        <v>100</v>
-      </c>
       <c r="F20" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G20" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>800</v>
+        <v>980</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>460</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>54</v>
@@ -1763,70 +1796,70 @@
         <v>56</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15">
       <c r="A21" s="13">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B21" s="14">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C21" s="14">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D21" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E21" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F21" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G21" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="14">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>1040</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>54</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15">
       <c r="A22" s="13">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B22" s="14">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C22" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D22" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E22" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F22" s="14">
         <v>300</v>
@@ -1835,15 +1868,15 @@
         <v>6</v>
       </c>
       <c r="H22" s="14">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>54</v>
@@ -1855,87 +1888,87 @@
         <v>61</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15">
       <c r="A23" s="13">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="14">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="C23" s="14">
         <v>120</v>
       </c>
       <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
         <v>90</v>
       </c>
-      <c r="E23" s="14">
-        <v>50</v>
-      </c>
       <c r="F23" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>290</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>58</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15">
       <c r="A24" s="13">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="14">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="C24" s="14">
         <v>120</v>
       </c>
       <c r="D24" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E24" s="14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F24" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G24" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H24" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>980</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>460</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>58</v>
@@ -1947,70 +1980,70 @@
         <v>56</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15">
       <c r="A25" s="13">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B25" s="14">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="C25" s="14">
         <v>120</v>
       </c>
       <c r="D25" s="14">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E25" s="14">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F25" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G25" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>1020</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>58</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15">
       <c r="A26" s="13">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B26" s="14">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="C26" s="14">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E26" s="14">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
         <v>0</v>
@@ -2019,179 +2052,179 @@
         <v>0</v>
       </c>
       <c r="H26" s="14">
-        <v>230</v>
+        <v>440</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15">
       <c r="A27" s="13">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B27" s="14">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="C27" s="14">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D27" s="14">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="E27" s="14">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="F27" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G27" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>440</v>
+        <v>360</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1310</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>130</v>
       </c>
       <c r="K27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15">
       <c r="A28" s="13">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B28" s="14">
         <v>340</v>
       </c>
       <c r="C28" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D28" s="14">
+        <v>90</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
         <v>130</v>
-      </c>
-      <c r="E28" s="14">
-        <v>130</v>
-      </c>
-      <c r="F28" s="14">
-        <v>250</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
-      <c r="H28" s="14">
-        <v>360</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1310</v>
+        <v>1040</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>54</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M28" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15">
       <c r="A29" s="13">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B29" s="14">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="C29" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D29" s="14">
+        <v>80</v>
+      </c>
+      <c r="E29" s="14">
         <v>90</v>
       </c>
-      <c r="E29" s="14">
-        <v>60</v>
-      </c>
       <c r="F29" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" s="14">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1160</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>280</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15">
       <c r="A30" s="13">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="14">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C30" s="14">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D30" s="14">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E30" s="14">
         <v>90</v>
@@ -2203,38 +2236,38 @@
         <v>5</v>
       </c>
       <c r="H30" s="14">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1110</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="K30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="M30" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15">
       <c r="A31" s="13">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B31" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C31" s="14">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D31" s="14">
         <v>120</v>
@@ -2249,90 +2282,90 @@
         <v>5</v>
       </c>
       <c r="H31" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="K31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L31" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>56</v>
-      </c>
       <c r="N31" s="17" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15">
       <c r="A32" s="13">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B32" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C32" s="14">
+        <v>120</v>
+      </c>
+      <c r="D32" s="14">
         <v>140</v>
       </c>
-      <c r="D32" s="14">
-        <v>120</v>
-      </c>
       <c r="E32" s="14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F32" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G32" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="14">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>920</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>520</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15">
       <c r="A33" s="13">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B33" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C33" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D33" s="14">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E33" s="14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F33" s="14">
         <v>0</v>
@@ -2341,64 +2374,64 @@
         <v>0</v>
       </c>
       <c r="H33" s="14">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>1015</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>425</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15">
       <c r="A34" s="13">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B34" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C34" s="14">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="D34" s="14">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="E34" s="14">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F34" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G34" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H34" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1015</v>
+        <v>1295</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>425</v>
+        <v>145</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="L34" s="16" t="s">
         <v>55</v>
@@ -2407,24 +2440,24 @@
         <v>56</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15">
       <c r="A35" s="13">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C35" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="D35" s="14">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E35" s="14">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="F35" s="14">
         <v>300</v>
@@ -2433,153 +2466,153 @@
         <v>6</v>
       </c>
       <c r="H35" s="14">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>54</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="15">
       <c r="A36" s="13">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B36" s="14">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C36" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
         <v>140</v>
       </c>
-      <c r="E36" s="14">
-        <v>120</v>
-      </c>
       <c r="F36" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G36" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H36" s="14">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1300</v>
+        <v>1290</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15">
       <c r="A37" s="13">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B37" s="14">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="C37" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D37" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E37" s="14">
         <v>140</v>
       </c>
       <c r="F37" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G37" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" s="14">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="15">
       <c r="A38" s="13">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B38" s="14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C38" s="14">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D38" s="14">
+        <v>140</v>
+      </c>
+      <c r="E38" s="14">
         <v>120</v>
       </c>
-      <c r="E38" s="14">
-        <v>140</v>
-      </c>
       <c r="F38" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G38" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H38" s="14">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>1300</v>
+        <v>1130</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>54</v>
@@ -2591,41 +2624,41 @@
         <v>56</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15">
       <c r="A39" s="13">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B39" s="14">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C39" s="14">
+        <v>100</v>
+      </c>
+      <c r="D39" s="14">
         <v>130</v>
       </c>
-      <c r="D39" s="14">
-        <v>140</v>
-      </c>
       <c r="E39" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F39" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G39" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" s="14">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>920</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>520</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>54</v>
@@ -2637,21 +2670,21 @@
         <v>56</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15">
       <c r="A40" s="13">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B40" s="14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C40" s="14">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D40" s="14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E40" s="14">
         <v>90</v>
@@ -2663,61 +2696,61 @@
         <v>0</v>
       </c>
       <c r="H40" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>54</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15">
       <c r="A41" s="13">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B41" s="14">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C41" s="14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D41" s="14">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E41" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F41" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G41" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H41" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>1220</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>220</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>54</v>
@@ -2726,10 +2759,10 @@
         <v>58</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -3336,11 +3369,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3358,11 +3391,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -4744,11 +4777,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I133:I196" si="4">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4766,11 +4799,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -6152,11 +6185,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I197:I260" si="6">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6174,11 +6207,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -7560,11 +7593,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I261:I324" si="8">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7582,11 +7615,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8968,11 +9001,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I325:I388" si="10">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8990,11 +9023,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -10376,11 +10409,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I389:I452" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J389:J452" si="13">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10398,11 +10431,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I453" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J453" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10630,28 +10663,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
+    <row r="401" ht="15"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10661,21 +10673,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J400">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
